--- a/important_mails_2026-08-19.xlsx
+++ b/important_mails_2026-08-19.xlsx
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -898,122 +898,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 12:15:45 +0000</t>
+          <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (tynmf1KRa8)</t>
+          <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
+ fireside chat</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-0080378-8359167
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1196270331805994</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 12 Aug 2026 05:20:43 +0000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
- fireside chat</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -1026,39 +926,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1075,39 +975,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1127,39 +1027,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:39:43 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1179,39 +1079,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:38:59 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1228,39 +1128,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:50 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1277,39 +1177,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 10:11:23 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1329,39 +1229,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 07:03:07 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -1390,40 +1290,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 13:25:55 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Did you catch Mary Beth's message? Early-bird extension ends August
  29</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-07/7z543yq/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z543yt/6828853872/h/09uV_tsw5XUFTzEZF_b-1pdSpEuhEDbCowtX9OlIcwk)
@@ -1437,39 +1337,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:57 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1486,39 +1386,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1538,86 +1438,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 12 Aug 2026 13:10:07 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Hear from sellers who've been to Accelerate—92.9% of sellers said it was worth it</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-11/7z56gp4/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
-[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
-​Sellers share their experience
-​​You've heard us talk about Amazon Accelerate. Now hear it from sellers who've actually been there.​​​
-In case you missed it, early-bird pricing has been extended through August 29! Save $100 and experience Accelerate 2026 for yourself.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
-Watch these Accelerate experience videos:
-[An image showcasing the key elements of a product listing page.](https://go.amazonsellerservices.com/e/229492/watch-v-UYDBZyysioA/7z56gpb/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
-[An image showcasing the key elements of a product listing page.](https://go.amazonsellerservices.com/e/229492/watch-v-htHY-VVc3mE/7z56gpf/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
-​​​92.9% of 2025 atten</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 10:06:05 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -1644,39 +1497,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 16:08:49 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1694,39 +1547,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 13 Aug 2026 04:08:25 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1744,39 +1597,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 12 Aug 2026 16:13:04 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Update tax information to prepare for UAE e-invoicing requirements</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Update tax information to prepare for UAE e-invoicing requirements
@@ -1791,39 +1644,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 00:28:18 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -1853,39 +1706,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 13:40:40 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1900,39 +1753,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:39:40 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Actualización de estado de mercancías peligrosas
@@ -1953,39 +1806,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:36:13 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -2006,39 +1859,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:35:04 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知（请勿回复） &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>危险品状态更新</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  危险品状态更新
@@ -2086,39 +1939,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:28:59 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Statusuppdatering för farligt gods</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Statusuppdatering för farligt gods
@@ -2140,39 +1993,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:03:40 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Aggiornamento dello stato delle merci pericolose
@@ -2193,39 +2046,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:03:04 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Update van status gevaarlijke goederen</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Update van status gevaarlijke goederen
@@ -2246,39 +2099,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 15 Aug 2026 04:15:54 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-08-27</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2302,39 +2155,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:35:04 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -2357,39 +2210,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 14 Aug 2026 01:27:02 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Mise à jour du statut de matières dangereuses</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Mise à jour du statut de matières dangereuses
@@ -2410,39 +2263,139 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 12:15:45 +0000</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (tynmf1KRa8)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-0080378-8359167
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1196270331805994</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 05:20:43 +0000</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:46:43 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (m4n18h8HiD)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2467,39 +2420,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 11 Aug 2026 05:00:42 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2515,39 +2468,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 09:16:35 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2563,39 +2516,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 14:33:13 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $126.79 in an attempt to settle your Amazon seller account balance.
@@ -2611,39 +2564,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 9 Aug 2026 04:49:49 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2659,39 +2612,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 14:11:22 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2712,39 +2665,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 8 Aug 2026 05:00:20 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2760,39 +2713,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 17:55:17 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2813,39 +2766,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 7 Aug 2026 04:52:01 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2861,39 +2814,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 17:19:22 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (PLBovnqz6i)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2913,39 +2866,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 6 Aug 2026 05:43:06 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2961,39 +2914,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 4 Aug 2026 04:57:39 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3009,39 +2962,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3061,39 +3014,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3109,39 +3062,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3157,39 +3110,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3205,39 +3158,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 09:23:20 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3253,39 +3206,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 19:42:31 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YsvR7aqoWy)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3310,39 +3263,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 07:19:03 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (8AOhKJjKS4)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3362,39 +3315,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 05:45:50 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3410,39 +3363,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:56:25 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.sa" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -3458,39 +3411,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:49:41 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.fr" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Account Protection</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon Seller Account Protection
@@ -3507,39 +3460,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:48:37 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ae" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -3555,39 +3508,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:43:00 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -3603,39 +3556,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:38:29 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -3651,39 +3604,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 14:56:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3704,39 +3657,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 05:51:10 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3752,39 +3705,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 09:53:48 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (WXuXOpUPId)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3809,39 +3762,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 06:03:52 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3857,39 +3810,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 16:41:05 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (ckaicj9NPD)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3909,39 +3862,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 09:48:04 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3957,39 +3910,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 04:57:36 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4005,39 +3958,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 20:49:44 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1pqaY5uvK2)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4062,39 +4015,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:44:02 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $63.02 in an attempt to settle your Amazon seller account balance.
@@ -4110,39 +4063,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:57:25 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4158,39 +4111,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 05:07:54 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4206,39 +4159,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 16:10:45 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -4254,39 +4207,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 10:35:17 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Zx1U3/hDuM)</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4306,39 +4259,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 05:01:14 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4354,39 +4307,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 05:03:32 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4402,39 +4355,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4450,39 +4403,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4498,39 +4451,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 06:15:19 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -4563,40 +4516,40 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:09:39 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Verstrek KYC-verificatie binnen 45 dagen om beperkingen te
  voorkomen</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Verstrek KYC-verificatie binnen 45 dagen om beperkingen te voorkomen
@@ -4615,39 +4568,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:52:41 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -4666,39 +4619,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:42:14 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -4717,39 +4670,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:24:08 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Fournissez une vérification KYC sous 45 jours pour éviter les restrictions</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Fournissez une vérification KYC sous 45 jours pour éviter les restrictions
@@ -4765,39 +4718,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -4814,39 +4767,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -4884,39 +4837,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:31:05 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -4933,39 +4886,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -5003,39 +4956,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5049,6 +5002,53 @@
  We’re here to help.
  If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
  For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 13:10:07 +0000</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Hear from sellers who've been to Accelerate—92.9% of sellers said it was worth it</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-11/7z56gp4/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
+​Sellers share their experience
+​​You've heard us talk about Amazon Accelerate. Now hear it from sellers who've actually been there.​​​
+In case you missed it, early-bird pricing has been extended through August 29! Save $100 and experience Accelerate 2026 for yourself.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z56gp7/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
+Watch these Accelerate experience videos:
+[An image showcasing the key elements of a product listing page.](https://go.amazonsellerservices.com/e/229492/watch-v-UYDBZyysioA/7z56gpb/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
+[An image showcasing the key elements of a product listing page.](https://go.amazonsellerservices.com/e/229492/watch-v-htHY-VVc3mE/7z56gpf/6826508754/h/QiUyqAFaZJ8bybuETp2Zaj1aeQqep5gBwkvyQ1nNdro)
+​​​92.9% of 2025 atten</t>
         </is>
       </c>
     </row>
